--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.8710765277629</v>
+        <v>9.404049935761472</v>
       </c>
       <c r="D2" t="n">
-        <v>50.38453677740858</v>
+        <v>8.187487226328896</v>
       </c>
       <c r="E2" t="n">
-        <v>19.70604605201675</v>
+        <v>3.202232483452722</v>
       </c>
       <c r="F2" t="n">
-        <v>18.197414480581</v>
+        <v>2.957079853094412</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.32086749743361</v>
+        <v>1.677140968332962</v>
       </c>
       <c r="D3" t="n">
-        <v>10.09809024214458</v>
+        <v>1.640939664348495</v>
       </c>
       <c r="E3" t="n">
-        <v>19.70604605201675</v>
+        <v>3.202232483452722</v>
       </c>
       <c r="F3" t="n">
-        <v>18.197414480581</v>
+        <v>2.957079853094412</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.05584975037446</v>
+        <v>4.559075584435851</v>
       </c>
       <c r="D4" t="n">
-        <v>28.28294585175868</v>
+        <v>4.595978700910786</v>
       </c>
       <c r="E4" t="n">
-        <v>19.70604605201675</v>
+        <v>3.202232483452722</v>
       </c>
       <c r="F4" t="n">
-        <v>18.197414480581</v>
+        <v>2.957079853094412</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.37761319332477</v>
+        <v>4.611362143915275</v>
       </c>
       <c r="D5" t="n">
-        <v>28.38474358798391</v>
+        <v>4.612520833047386</v>
       </c>
       <c r="E5" t="n">
-        <v>19.70604605201675</v>
+        <v>3.202232483452722</v>
       </c>
       <c r="F5" t="n">
-        <v>18.197414480581</v>
+        <v>2.957079853094412</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.3545999199163</v>
+        <v>6.720122486986399</v>
       </c>
       <c r="D6" t="n">
-        <v>39.85451853405733</v>
+        <v>6.476359261784316</v>
       </c>
       <c r="E6" t="n">
-        <v>19.70604605201675</v>
+        <v>3.202232483452722</v>
       </c>
       <c r="F6" t="n">
-        <v>18.197414480581</v>
+        <v>2.957079853094412</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.52414854736185</v>
+        <v>6.5851741389463</v>
       </c>
       <c r="D7" t="n">
-        <v>40.35306246805019</v>
+        <v>6.557372651058156</v>
       </c>
       <c r="E7" t="n">
-        <v>19.70604605201675</v>
+        <v>3.202232483452722</v>
       </c>
       <c r="F7" t="n">
-        <v>18.197414480581</v>
+        <v>2.957079853094412</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>3.108364291924606</v>
+        <v>0.5051091974377485</v>
       </c>
       <c r="D8" t="n">
-        <v>7.315306162234772</v>
+        <v>1.18873725136315</v>
       </c>
       <c r="E8" t="n">
-        <v>19.70604605201675</v>
+        <v>3.202232483452722</v>
       </c>
       <c r="F8" t="n">
-        <v>18.197414480581</v>
+        <v>2.957079853094412</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.43109508486133</v>
+        <v>5.107552951289966</v>
       </c>
       <c r="D9" t="n">
-        <v>31.26753727553097</v>
+        <v>5.080974807273782</v>
       </c>
       <c r="E9" t="n">
-        <v>19.70604605201675</v>
+        <v>3.202232483452722</v>
       </c>
       <c r="F9" t="n">
-        <v>18.197414480581</v>
+        <v>2.957079853094412</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.41793720956488</v>
+        <v>4.130414796554293</v>
       </c>
       <c r="D10" t="n">
-        <v>25.39973979371217</v>
+        <v>4.127457716478228</v>
       </c>
       <c r="E10" t="n">
-        <v>19.70604605201675</v>
+        <v>3.202232483452722</v>
       </c>
       <c r="F10" t="n">
-        <v>18.197414480581</v>
+        <v>2.957079853094412</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>73.42855648158096</v>
+        <v>11.93214042825691</v>
       </c>
       <c r="D11" t="n">
-        <v>73.2715081534936</v>
+        <v>11.90662007494271</v>
       </c>
       <c r="E11" t="n">
-        <v>19.70604605201675</v>
+        <v>3.202232483452722</v>
       </c>
       <c r="F11" t="n">
-        <v>18.197414480581</v>
+        <v>2.957079853094412</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
